--- a/AAII_Financials/Yearly/ZHUZY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ZHUZY_YR_FIN.xlsx
@@ -1745,7 +1745,7 @@
         <v>384600</v>
       </c>
       <c r="F47" s="3">
-        <v>108100</v>
+        <v>608000</v>
       </c>
       <c r="G47" s="3">
         <v>568600</v>
@@ -1895,7 +1895,7 @@
         <v>88000</v>
       </c>
       <c r="F52" s="3">
-        <v>675500</v>
+        <v>175600</v>
       </c>
       <c r="G52" s="3">
         <v>52200</v>
